--- a/blog/templates/decision-matrix-template/decision-matrix.xlsx
+++ b/blog/templates/decision-matrix-template/decision-matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision matrix" sheetId="1" r:id="R8621ef70f5dc45e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked example" sheetId="2" r:id="Re4ff909896d4447a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision matrix" sheetId="1" r:id="R9ebb0450cb734a42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked example" sheetId="2" r:id="R3b70b1366be34a28"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1134,7 +1134,7 @@
         <x:v>Final choice and reason</x:v>
       </x:c>
       <x:c r="C26" s="13" t="str">
-        <x:v>No real decision. Option B has the highest total under these inputs.</x:v>
+        <x:v>Illustrative example only. Record a real choice after reviewing your inputs.</x:v>
       </x:c>
       <x:c r="D26" s="13"/>
       <x:c r="E26" s="13"/>
